--- a/results/calibration/y-factors/ZAF_calibration.xlsx
+++ b/results/calibration/y-factors/ZAF_calibration.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute.sharepoint.com/sites/WG-Modelling-HCVvaccinemodel/Shared Documents/HCV vaccine model/HCV vaccine model/results/calibration/y-factors/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_387303E47135986EEF9C693DF8E9B1932DA0936D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3A64FF-B58B-4C0D-A239-562074512DEA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Y-factors" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="304">
   <si>
     <t>meta_y_factor</t>
   </si>
@@ -589,6 +583,9 @@
     <t>vaccine_waning_dur</t>
   </si>
   <si>
+    <t>vaccine_prop_clear_initial</t>
+  </si>
+  <si>
     <t>vaccine_prop_clear</t>
   </si>
   <si>
@@ -601,6 +598,12 @@
     <t>vaccine_infx_mult_gen</t>
   </si>
   <si>
+    <t>acute_vax_initial</t>
+  </si>
+  <si>
+    <t>acute_vax_reinfected</t>
+  </si>
+  <si>
     <t>sus_abneg_vax</t>
   </si>
   <si>
@@ -896,6 +899,9 @@
   </si>
   <si>
     <t>cc_cured</t>
+  </si>
+  <si>
+    <t>vaccine_prop_chronic_initial</t>
   </si>
   <si>
     <t>vaccine_prop_chronic</t>
@@ -925,8 +931,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,21 +995,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1041,7 +1039,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1075,7 +1073,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1110,10 +1107,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1286,11 +1282,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O302"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O306"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1337,7 +1333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1382,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1427,7 +1423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1517,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1562,7 +1558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1607,7 +1603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1652,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1697,7 +1693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1742,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1787,7 +1783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1832,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1877,7 +1873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1922,7 +1918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1967,7 +1963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -2012,7 +2008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -2057,7 +2053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -2102,19 +2098,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>3.805868548154831</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>9.00454179868102</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2141,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="O19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
@@ -2192,7 +2188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -2237,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -2327,7 +2323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2372,7 +2368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
@@ -2417,7 +2413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
@@ -2462,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
@@ -2507,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="A28" s="1" t="s">
         <v>41</v>
       </c>
@@ -2552,7 +2548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -2597,7 +2593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
@@ -2642,7 +2638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,7 +2683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -2732,7 +2728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" s="1" t="s">
         <v>46</v>
       </c>
@@ -2777,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -2822,7 +2818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -2867,7 +2863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15">
       <c r="A36" s="1" t="s">
         <v>49</v>
       </c>
@@ -2912,7 +2908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15">
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
@@ -2957,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15">
       <c r="A38" s="1" t="s">
         <v>51</v>
       </c>
@@ -3002,7 +2998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15">
       <c r="A39" s="1" t="s">
         <v>52</v>
       </c>
@@ -3047,7 +3043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
@@ -3092,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15">
       <c r="A41" s="1" t="s">
         <v>54</v>
       </c>
@@ -3137,7 +3133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -3182,7 +3178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,7 +3223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -3272,7 +3268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
@@ -3317,7 +3313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -3362,7 +3358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -3407,7 +3403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -3452,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
@@ -3497,7 +3493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50" s="1" t="s">
         <v>63</v>
       </c>
@@ -3542,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
@@ -3587,7 +3583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
@@ -3632,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -3677,7 +3673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
@@ -3722,7 +3718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -3767,7 +3763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -3812,13 +3808,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3857,13 +3853,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3902,13 +3898,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3947,13 +3943,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3992,7 +3988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
@@ -4037,7 +4033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -4082,7 +4078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,7 +4123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
@@ -4172,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
@@ -4217,7 +4213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
@@ -4262,7 +4258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15">
       <c r="A67" s="1" t="s">
         <v>80</v>
       </c>
@@ -4307,7 +4303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15">
       <c r="A68" s="1" t="s">
         <v>81</v>
       </c>
@@ -4352,7 +4348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15">
       <c r="A69" s="1" t="s">
         <v>82</v>
       </c>
@@ -4397,7 +4393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15">
       <c r="A70" s="1" t="s">
         <v>83</v>
       </c>
@@ -4442,7 +4438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15">
       <c r="A71" s="1" t="s">
         <v>84</v>
       </c>
@@ -4487,7 +4483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15">
       <c r="A72" s="1" t="s">
         <v>85</v>
       </c>
@@ -4532,7 +4528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15">
       <c r="A73" s="1" t="s">
         <v>86</v>
       </c>
@@ -4577,7 +4573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15">
       <c r="A74" s="1" t="s">
         <v>87</v>
       </c>
@@ -4622,7 +4618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15">
       <c r="A75" s="1" t="s">
         <v>88</v>
       </c>
@@ -4667,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15">
       <c r="A76" s="1" t="s">
         <v>89</v>
       </c>
@@ -4712,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15">
       <c r="A77" s="1" t="s">
         <v>90</v>
       </c>
@@ -4757,7 +4753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15">
       <c r="A78" s="1" t="s">
         <v>91</v>
       </c>
@@ -4802,7 +4798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15">
       <c r="A79" s="1" t="s">
         <v>92</v>
       </c>
@@ -4847,7 +4843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15">
       <c r="A80" s="1" t="s">
         <v>93</v>
       </c>
@@ -4892,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15">
       <c r="A81" s="1" t="s">
         <v>94</v>
       </c>
@@ -4937,7 +4933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15">
       <c r="A82" s="1" t="s">
         <v>95</v>
       </c>
@@ -4982,7 +4978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15">
       <c r="A83" s="1" t="s">
         <v>96</v>
       </c>
@@ -5027,7 +5023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15">
       <c r="A84" s="1" t="s">
         <v>97</v>
       </c>
@@ -5072,7 +5068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15">
       <c r="A85" s="1" t="s">
         <v>98</v>
       </c>
@@ -5117,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15">
       <c r="A86" s="1" t="s">
         <v>99</v>
       </c>
@@ -5162,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15">
       <c r="A87" s="1" t="s">
         <v>100</v>
       </c>
@@ -5207,7 +5203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15">
       <c r="A88" s="1" t="s">
         <v>101</v>
       </c>
@@ -5252,7 +5248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15">
       <c r="A89" s="1" t="s">
         <v>102</v>
       </c>
@@ -5297,7 +5293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15">
       <c r="A90" s="1" t="s">
         <v>103</v>
       </c>
@@ -5342,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15">
       <c r="A91" s="1" t="s">
         <v>104</v>
       </c>
@@ -5387,7 +5383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15">
       <c r="A92" s="1" t="s">
         <v>105</v>
       </c>
@@ -5432,7 +5428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15">
       <c r="A93" s="1" t="s">
         <v>106</v>
       </c>
@@ -5477,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15">
       <c r="A94" s="1" t="s">
         <v>107</v>
       </c>
@@ -5522,7 +5518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15">
       <c r="A95" s="1" t="s">
         <v>108</v>
       </c>
@@ -5567,7 +5563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15">
       <c r="A96" s="1" t="s">
         <v>109</v>
       </c>
@@ -5612,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15">
       <c r="A97" s="1" t="s">
         <v>110</v>
       </c>
@@ -5657,7 +5653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15">
       <c r="A98" s="1" t="s">
         <v>111</v>
       </c>
@@ -5702,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15">
       <c r="A99" s="1" t="s">
         <v>112</v>
       </c>
@@ -5747,7 +5743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15">
       <c r="A100" s="1" t="s">
         <v>113</v>
       </c>
@@ -5792,7 +5788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15">
       <c r="A101" s="1" t="s">
         <v>114</v>
       </c>
@@ -5837,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15">
       <c r="A102" s="1" t="s">
         <v>115</v>
       </c>
@@ -5882,7 +5878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15">
       <c r="A103" s="1" t="s">
         <v>116</v>
       </c>
@@ -5927,7 +5923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15">
       <c r="A104" s="1" t="s">
         <v>117</v>
       </c>
@@ -5972,7 +5968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
@@ -6017,7 +6013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
@@ -6062,7 +6058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -6107,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -6152,7 +6148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15">
       <c r="A109" s="1" t="s">
         <v>122</v>
       </c>
@@ -6197,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -6242,7 +6238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -6287,7 +6283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -6332,7 +6328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15">
       <c r="A113" s="1" t="s">
         <v>126</v>
       </c>
@@ -6377,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15">
       <c r="A114" s="1" t="s">
         <v>127</v>
       </c>
@@ -6422,7 +6418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15">
       <c r="A115" s="1" t="s">
         <v>128</v>
       </c>
@@ -6467,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15">
       <c r="A116" s="1" t="s">
         <v>129</v>
       </c>
@@ -6512,7 +6508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -6557,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -6602,7 +6598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15">
       <c r="A119" s="1" t="s">
         <v>132</v>
       </c>
@@ -6647,7 +6643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15">
       <c r="A120" s="1" t="s">
         <v>133</v>
       </c>
@@ -6692,7 +6688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15">
       <c r="A121" s="1" t="s">
         <v>134</v>
       </c>
@@ -6737,7 +6733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15">
       <c r="A122" s="1" t="s">
         <v>135</v>
       </c>
@@ -6782,7 +6778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15">
       <c r="A123" s="1" t="s">
         <v>136</v>
       </c>
@@ -6827,7 +6823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15">
       <c r="A124" s="1" t="s">
         <v>137</v>
       </c>
@@ -6872,7 +6868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15">
       <c r="A125" s="1" t="s">
         <v>138</v>
       </c>
@@ -6917,7 +6913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15">
       <c r="A126" s="1" t="s">
         <v>139</v>
       </c>
@@ -6962,7 +6958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15">
       <c r="A127" s="1" t="s">
         <v>140</v>
       </c>
@@ -7007,7 +7003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15">
       <c r="A128" s="1" t="s">
         <v>141</v>
       </c>
@@ -7052,7 +7048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15">
       <c r="A129" s="1" t="s">
         <v>142</v>
       </c>
@@ -7097,7 +7093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15">
       <c r="A130" s="1" t="s">
         <v>143</v>
       </c>
@@ -7142,7 +7138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15">
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
@@ -7187,7 +7183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15">
       <c r="A132" s="1" t="s">
         <v>145</v>
       </c>
@@ -7232,7 +7228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15">
       <c r="A133" s="1" t="s">
         <v>146</v>
       </c>
@@ -7277,7 +7273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15">
       <c r="A134" s="1" t="s">
         <v>147</v>
       </c>
@@ -7322,7 +7318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -7367,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -7412,7 +7408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15">
       <c r="A137" s="1" t="s">
         <v>150</v>
       </c>
@@ -7457,7 +7453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15">
       <c r="A138" s="1" t="s">
         <v>151</v>
       </c>
@@ -7502,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15">
       <c r="A139" s="1" t="s">
         <v>152</v>
       </c>
@@ -7547,7 +7543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -7592,7 +7588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15">
       <c r="A141" s="1" t="s">
         <v>154</v>
       </c>
@@ -7637,7 +7633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
@@ -7682,7 +7678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15">
       <c r="A143" s="1" t="s">
         <v>156</v>
       </c>
@@ -7727,7 +7723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15">
       <c r="A144" s="1" t="s">
         <v>157</v>
       </c>
@@ -7772,7 +7768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15">
       <c r="A145" s="1" t="s">
         <v>158</v>
       </c>
@@ -7817,7 +7813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15">
       <c r="A146" s="1" t="s">
         <v>159</v>
       </c>
@@ -7862,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15">
       <c r="A147" s="1" t="s">
         <v>160</v>
       </c>
@@ -7907,7 +7903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15">
       <c r="A148" s="1" t="s">
         <v>161</v>
       </c>
@@ -7952,7 +7948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15">
       <c r="A149" s="1" t="s">
         <v>162</v>
       </c>
@@ -7997,7 +7993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15">
       <c r="A150" s="1" t="s">
         <v>163</v>
       </c>
@@ -8042,7 +8038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15">
       <c r="A151" s="1" t="s">
         <v>164</v>
       </c>
@@ -8087,7 +8083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15">
       <c r="A152" s="1" t="s">
         <v>165</v>
       </c>
@@ -8132,7 +8128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15">
       <c r="A153" s="1" t="s">
         <v>166</v>
       </c>
@@ -8177,7 +8173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -8222,7 +8218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15">
       <c r="A155" s="1" t="s">
         <v>168</v>
       </c>
@@ -8267,7 +8263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15">
       <c r="A156" s="1" t="s">
         <v>169</v>
       </c>
@@ -8312,7 +8308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15">
       <c r="A157" s="1" t="s">
         <v>170</v>
       </c>
@@ -8357,7 +8353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15">
       <c r="A158" s="1" t="s">
         <v>171</v>
       </c>
@@ -8402,7 +8398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15">
       <c r="A159" s="1" t="s">
         <v>172</v>
       </c>
@@ -8447,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15">
       <c r="A160" s="1" t="s">
         <v>173</v>
       </c>
@@ -8492,7 +8488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15">
       <c r="A161" s="1" t="s">
         <v>174</v>
       </c>
@@ -8537,7 +8533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15">
       <c r="A162" s="1" t="s">
         <v>175</v>
       </c>
@@ -8582,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15">
       <c r="A163" s="1" t="s">
         <v>176</v>
       </c>
@@ -8627,7 +8623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15">
       <c r="A164" s="1" t="s">
         <v>177</v>
       </c>
@@ -8672,7 +8668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15">
       <c r="A165" s="1" t="s">
         <v>178</v>
       </c>
@@ -8717,7 +8713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15">
       <c r="A166" s="1" t="s">
         <v>179</v>
       </c>
@@ -8762,7 +8758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15">
       <c r="A167" s="1" t="s">
         <v>180</v>
       </c>
@@ -8807,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15">
       <c r="A168" s="1" t="s">
         <v>181</v>
       </c>
@@ -8852,13 +8848,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15">
       <c r="A169" s="1" t="s">
         <v>182</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169">
-        <v>0.22185668945312489</v>
+        <v>0.2231201171874999</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -8897,13 +8893,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15">
       <c r="A170" s="1" t="s">
         <v>183</v>
       </c>
       <c r="B170" s="1"/>
       <c r="C170">
-        <v>9.5351562500000001E-2</v>
+        <v>0.0933251953125</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -8942,7 +8938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15">
       <c r="A171" s="1" t="s">
         <v>184</v>
       </c>
@@ -8987,7 +8983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15">
       <c r="A172" s="1" t="s">
         <v>185</v>
       </c>
@@ -9032,7 +9028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15">
       <c r="A173" s="1" t="s">
         <v>186</v>
       </c>
@@ -9077,7 +9073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15">
       <c r="A174" s="1" t="s">
         <v>187</v>
       </c>
@@ -9122,7 +9118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15">
       <c r="A175" s="1" t="s">
         <v>188</v>
       </c>
@@ -9167,7 +9163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15">
       <c r="A176" s="1" t="s">
         <v>189</v>
       </c>
@@ -9212,7 +9208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15">
       <c r="A177" s="1" t="s">
         <v>190</v>
       </c>
@@ -9257,7 +9253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15">
       <c r="A178" s="1" t="s">
         <v>191</v>
       </c>
@@ -9302,7 +9298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15">
       <c r="A179" s="1" t="s">
         <v>192</v>
       </c>
@@ -9347,7 +9343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15">
       <c r="A180" s="1" t="s">
         <v>193</v>
       </c>
@@ -9392,7 +9388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15">
       <c r="A181" s="1" t="s">
         <v>194</v>
       </c>
@@ -9437,7 +9433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15">
       <c r="A182" s="1" t="s">
         <v>195</v>
       </c>
@@ -9482,7 +9478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15">
       <c r="A183" s="1" t="s">
         <v>196</v>
       </c>
@@ -9527,7 +9523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15">
       <c r="A184" s="1" t="s">
         <v>197</v>
       </c>
@@ -9572,7 +9568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15">
       <c r="A185" s="1" t="s">
         <v>198</v>
       </c>
@@ -9617,7 +9613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15">
       <c r="A186" s="1" t="s">
         <v>199</v>
       </c>
@@ -9662,7 +9658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15">
       <c r="A187" s="1" t="s">
         <v>200</v>
       </c>
@@ -9707,7 +9703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15">
       <c r="A188" s="1" t="s">
         <v>201</v>
       </c>
@@ -9752,7 +9748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15">
       <c r="A189" s="1" t="s">
         <v>202</v>
       </c>
@@ -9797,7 +9793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15">
       <c r="A190" s="1" t="s">
         <v>203</v>
       </c>
@@ -9842,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15">
       <c r="A191" s="1" t="s">
         <v>204</v>
       </c>
@@ -9887,7 +9883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15">
       <c r="A192" s="1" t="s">
         <v>205</v>
       </c>
@@ -9932,7 +9928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15">
       <c r="A193" s="1" t="s">
         <v>206</v>
       </c>
@@ -9977,7 +9973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15">
       <c r="A194" s="1" t="s">
         <v>207</v>
       </c>
@@ -10022,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15">
       <c r="A195" s="1" t="s">
         <v>208</v>
       </c>
@@ -10067,7 +10063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15">
       <c r="A196" s="1" t="s">
         <v>209</v>
       </c>
@@ -10112,7 +10108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15">
       <c r="A197" s="1" t="s">
         <v>210</v>
       </c>
@@ -10157,7 +10153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15">
       <c r="A198" s="1" t="s">
         <v>211</v>
       </c>
@@ -10202,7 +10198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15">
       <c r="A199" s="1" t="s">
         <v>212</v>
       </c>
@@ -10247,7 +10243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15">
       <c r="A200" s="1" t="s">
         <v>213</v>
       </c>
@@ -10292,7 +10288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15">
       <c r="A201" s="1" t="s">
         <v>214</v>
       </c>
@@ -10337,7 +10333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15">
       <c r="A202" s="1" t="s">
         <v>215</v>
       </c>
@@ -10382,7 +10378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15">
       <c r="A203" s="1" t="s">
         <v>216</v>
       </c>
@@ -10427,7 +10423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15">
       <c r="A204" s="1" t="s">
         <v>217</v>
       </c>
@@ -10472,7 +10468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15">
       <c r="A205" s="1" t="s">
         <v>218</v>
       </c>
@@ -10517,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15">
       <c r="A206" s="1" t="s">
         <v>219</v>
       </c>
@@ -10562,7 +10558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15">
       <c r="A207" s="1" t="s">
         <v>220</v>
       </c>
@@ -10607,7 +10603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15">
       <c r="A208" s="1" t="s">
         <v>221</v>
       </c>
@@ -10652,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15">
       <c r="A209" s="1" t="s">
         <v>222</v>
       </c>
@@ -10697,7 +10693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15">
       <c r="A210" s="1" t="s">
         <v>223</v>
       </c>
@@ -10742,7 +10738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15">
       <c r="A211" s="1" t="s">
         <v>224</v>
       </c>
@@ -10787,7 +10783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15">
       <c r="A212" s="1" t="s">
         <v>225</v>
       </c>
@@ -10832,7 +10828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15">
       <c r="A213" s="1" t="s">
         <v>226</v>
       </c>
@@ -10877,7 +10873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15">
       <c r="A214" s="1" t="s">
         <v>227</v>
       </c>
@@ -10922,7 +10918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15">
       <c r="A215" s="1" t="s">
         <v>228</v>
       </c>
@@ -10967,7 +10963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15">
       <c r="A216" s="1" t="s">
         <v>229</v>
       </c>
@@ -11012,7 +11008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15">
       <c r="A217" s="1" t="s">
         <v>230</v>
       </c>
@@ -11057,7 +11053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15">
       <c r="A218" s="1" t="s">
         <v>231</v>
       </c>
@@ -11102,7 +11098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15">
       <c r="A219" s="1" t="s">
         <v>232</v>
       </c>
@@ -11147,7 +11143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15">
       <c r="A220" s="1" t="s">
         <v>233</v>
       </c>
@@ -11192,7 +11188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15">
       <c r="A221" s="1" t="s">
         <v>234</v>
       </c>
@@ -11237,7 +11233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15">
       <c r="A222" s="1" t="s">
         <v>235</v>
       </c>
@@ -11282,7 +11278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15">
       <c r="A223" s="1" t="s">
         <v>236</v>
       </c>
@@ -11327,7 +11323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15">
       <c r="A224" s="1" t="s">
         <v>237</v>
       </c>
@@ -11372,7 +11368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15">
       <c r="A225" s="1" t="s">
         <v>238</v>
       </c>
@@ -11417,7 +11413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15">
       <c r="A226" s="1" t="s">
         <v>239</v>
       </c>
@@ -11462,7 +11458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15">
       <c r="A227" s="1" t="s">
         <v>240</v>
       </c>
@@ -11507,7 +11503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15">
       <c r="A228" s="1" t="s">
         <v>241</v>
       </c>
@@ -11552,7 +11548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15">
       <c r="A229" s="1" t="s">
         <v>242</v>
       </c>
@@ -11597,7 +11593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15">
       <c r="A230" s="1" t="s">
         <v>243</v>
       </c>
@@ -11642,7 +11638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15">
       <c r="A231" s="1" t="s">
         <v>244</v>
       </c>
@@ -11687,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15">
       <c r="A232" s="1" t="s">
         <v>245</v>
       </c>
@@ -11732,7 +11728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15">
       <c r="A233" s="1" t="s">
         <v>246</v>
       </c>
@@ -11777,7 +11773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15">
       <c r="A234" s="1" t="s">
         <v>247</v>
       </c>
@@ -11822,7 +11818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15">
       <c r="A235" s="1" t="s">
         <v>248</v>
       </c>
@@ -11867,7 +11863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15">
       <c r="A236" s="1" t="s">
         <v>249</v>
       </c>
@@ -11912,7 +11908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15">
       <c r="A237" s="1" t="s">
         <v>250</v>
       </c>
@@ -11957,7 +11953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15">
       <c r="A238" s="1" t="s">
         <v>251</v>
       </c>
@@ -12002,7 +11998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15">
       <c r="A239" s="1" t="s">
         <v>252</v>
       </c>
@@ -12047,7 +12043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15">
       <c r="A240" s="1" t="s">
         <v>253</v>
       </c>
@@ -12092,7 +12088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15">
       <c r="A241" s="1" t="s">
         <v>254</v>
       </c>
@@ -12137,7 +12133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15">
       <c r="A242" s="1" t="s">
         <v>255</v>
       </c>
@@ -12182,7 +12178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15">
       <c r="A243" s="1" t="s">
         <v>256</v>
       </c>
@@ -12227,7 +12223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15">
       <c r="A244" s="1" t="s">
         <v>257</v>
       </c>
@@ -12272,7 +12268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15">
       <c r="A245" s="1" t="s">
         <v>258</v>
       </c>
@@ -12317,7 +12313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15">
       <c r="A246" s="1" t="s">
         <v>259</v>
       </c>
@@ -12362,7 +12358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15">
       <c r="A247" s="1" t="s">
         <v>260</v>
       </c>
@@ -12407,7 +12403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15">
       <c r="A248" s="1" t="s">
         <v>261</v>
       </c>
@@ -12452,7 +12448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15">
       <c r="A249" s="1" t="s">
         <v>262</v>
       </c>
@@ -12497,7 +12493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15">
       <c r="A250" s="1" t="s">
         <v>263</v>
       </c>
@@ -12542,7 +12538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15">
       <c r="A251" s="1" t="s">
         <v>264</v>
       </c>
@@ -12587,7 +12583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15">
       <c r="A252" s="1" t="s">
         <v>265</v>
       </c>
@@ -12632,7 +12628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15">
       <c r="A253" s="1" t="s">
         <v>266</v>
       </c>
@@ -12677,7 +12673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15">
       <c r="A254" s="1" t="s">
         <v>267</v>
       </c>
@@ -12722,7 +12718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15">
       <c r="A255" s="1" t="s">
         <v>268</v>
       </c>
@@ -12767,7 +12763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15">
       <c r="A256" s="1" t="s">
         <v>269</v>
       </c>
@@ -12812,7 +12808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15">
       <c r="A257" s="1" t="s">
         <v>270</v>
       </c>
@@ -12857,7 +12853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15">
       <c r="A258" s="1" t="s">
         <v>271</v>
       </c>
@@ -12902,7 +12898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15">
       <c r="A259" s="1" t="s">
         <v>272</v>
       </c>
@@ -12947,7 +12943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15">
       <c r="A260" s="1" t="s">
         <v>273</v>
       </c>
@@ -12992,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15">
       <c r="A261" s="1" t="s">
         <v>274</v>
       </c>
@@ -13037,7 +13033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15">
       <c r="A262" s="1" t="s">
         <v>275</v>
       </c>
@@ -13082,7 +13078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15">
       <c r="A263" s="1" t="s">
         <v>276</v>
       </c>
@@ -13127,7 +13123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15">
       <c r="A264" s="1" t="s">
         <v>277</v>
       </c>
@@ -13172,7 +13168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15">
       <c r="A265" s="1" t="s">
         <v>278</v>
       </c>
@@ -13217,7 +13213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15">
       <c r="A266" s="1" t="s">
         <v>279</v>
       </c>
@@ -13262,7 +13258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15">
       <c r="A267" s="1" t="s">
         <v>280</v>
       </c>
@@ -13307,7 +13303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15">
       <c r="A268" s="1" t="s">
         <v>281</v>
       </c>
@@ -13352,7 +13348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15">
       <c r="A269" s="1" t="s">
         <v>282</v>
       </c>
@@ -13397,7 +13393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15">
       <c r="A270" s="1" t="s">
         <v>283</v>
       </c>
@@ -13442,7 +13438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15">
       <c r="A271" s="1" t="s">
         <v>284</v>
       </c>
@@ -13487,7 +13483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15">
       <c r="A272" s="1" t="s">
         <v>285</v>
       </c>
@@ -13532,7 +13528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15">
       <c r="A273" s="1" t="s">
         <v>286</v>
       </c>
@@ -13577,7 +13573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15">
       <c r="A274" s="1" t="s">
         <v>287</v>
       </c>
@@ -13622,7 +13618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15">
       <c r="A275" s="1" t="s">
         <v>288</v>
       </c>
@@ -13667,7 +13663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15">
       <c r="A276" s="1" t="s">
         <v>289</v>
       </c>
@@ -13712,7 +13708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15">
       <c r="A277" s="1" t="s">
         <v>290</v>
       </c>
@@ -13757,7 +13753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15">
       <c r="A278" s="1" t="s">
         <v>291</v>
       </c>
@@ -13802,7 +13798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15">
       <c r="A279" s="1" t="s">
         <v>292</v>
       </c>
@@ -13847,7 +13843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15">
       <c r="A280" s="1" t="s">
         <v>293</v>
       </c>
@@ -13892,7 +13888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15">
       <c r="A281" s="1" t="s">
         <v>294</v>
       </c>
@@ -13937,7 +13933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15">
       <c r="A282" s="1" t="s">
         <v>295</v>
       </c>
@@ -13982,13 +13978,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15">
       <c r="A283" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B283" s="1"/>
       <c r="C283">
         <v>1</v>
       </c>
@@ -13998,157 +13992,283 @@
       <c r="E283">
         <v>1</v>
       </c>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>1</v>
+      </c>
+      <c r="N283">
+        <v>1</v>
+      </c>
+      <c r="O283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15">
       <c r="A284" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B284" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B284" s="1"/>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>1</v>
+      </c>
+      <c r="L284">
+        <v>1</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>1</v>
+      </c>
+      <c r="O284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15">
+      <c r="A285" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B285" s="1"/>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>1</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>1</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
+      <c r="N285">
+        <v>1</v>
+      </c>
+      <c r="O285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15">
+      <c r="A286" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B286" s="1"/>
+      <c r="C286">
+        <v>1</v>
+      </c>
+      <c r="D286">
+        <v>1</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>1</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286">
+        <v>1</v>
+      </c>
+      <c r="L286">
+        <v>1</v>
+      </c>
+      <c r="M286">
+        <v>1</v>
+      </c>
+      <c r="N286">
+        <v>1</v>
+      </c>
+      <c r="O286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15">
+      <c r="A287" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287">
+        <v>1</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15">
+      <c r="A288" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284">
-        <v>1</v>
-      </c>
-      <c r="E284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A285" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B285" s="1" t="s">
+      <c r="C288">
+        <v>1</v>
+      </c>
+      <c r="D288">
+        <v>1</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15">
+      <c r="A289" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="N285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A286" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B286" s="1" t="s">
+      <c r="C289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15">
+      <c r="A290" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C286">
-        <v>1</v>
-      </c>
-      <c r="O286">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A287" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B287" s="1" t="s">
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="O290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15">
+      <c r="A291" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="H287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A288" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B288" s="1" t="s">
+      <c r="C291">
+        <v>1</v>
+      </c>
+      <c r="H291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15">
+      <c r="A292" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C288">
-        <v>1</v>
-      </c>
-      <c r="I288">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B289" s="1" t="s">
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15">
+      <c r="A293" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C289">
-        <v>1</v>
-      </c>
-      <c r="J289">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A290" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B290" s="1" t="s">
+      <c r="C293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15">
+      <c r="A294" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C290">
-        <v>1</v>
-      </c>
-      <c r="K290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A291" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C291">
-        <v>1</v>
-      </c>
-      <c r="L291">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A292" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C292">
-        <v>1</v>
-      </c>
-      <c r="M292">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A293" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C293">
-        <v>1</v>
-      </c>
-      <c r="J293">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A294" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="C294">
         <v>1</v>
       </c>
@@ -14156,9 +14276,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15">
       <c r="A295" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>7</v>
@@ -14166,13 +14286,13 @@
       <c r="C295">
         <v>1</v>
       </c>
-      <c r="D295">
-        <v>1.6617797851562499</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15">
       <c r="A296" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>8</v>
@@ -14180,13 +14300,13 @@
       <c r="C296">
         <v>1</v>
       </c>
-      <c r="E296">
-        <v>1.35625</v>
-      </c>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15">
       <c r="A297" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>1</v>
@@ -14194,13 +14314,13 @@
       <c r="C297">
         <v>1</v>
       </c>
-      <c r="N297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15">
       <c r="A298" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>2</v>
@@ -14208,13 +14328,13 @@
       <c r="C298">
         <v>1</v>
       </c>
-      <c r="O298">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>7</v>
@@ -14222,13 +14342,13 @@
       <c r="C299">
         <v>1</v>
       </c>
-      <c r="N299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D299">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15">
       <c r="A300" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>8</v>
@@ -14236,272 +14356,101 @@
       <c r="C300">
         <v>1</v>
       </c>
-      <c r="O300">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E300">
+        <v>0.453608863428235</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15">
       <c r="A301" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15">
+      <c r="A302" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="O302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15">
+      <c r="A303" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15">
+      <c r="A304" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="O304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C301">
-        <v>1</v>
-      </c>
-      <c r="D301">
-        <v>1</v>
-      </c>
-      <c r="J301">
-        <v>0.98749999999999993</v>
-      </c>
-    </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B302" s="1" t="s">
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>0.7720703125</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11">
+      <c r="A306" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-      <c r="E302">
-        <v>1</v>
-      </c>
-      <c r="K302">
-        <v>0.89433593750000007</v>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+      <c r="K306">
+        <v>0.2432511866092681</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
-    <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="460e4ad2-c64b-4f67-8552-094351f252e3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9012861f-df9c-4ac0-92bd-da4c61c7cfda" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4719BD33-65BD-4353-A3EE-6F46DB1B3586}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10094608-D580-4CBF-98B8-CA73B2F88812}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9695EDD0-0777-463C-9396-B3530D3813A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>